--- a/file_operation/difflib/string_comparison/input_data/criteria_wb.xlsx
+++ b/file_operation/difflib/string_comparison/input_data/criteria_wb.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\develop\github\python_labo\file_operation\find_string_difflib\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\develop\github\python_labo\file_operation\difflib\string_comparison\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A31F535-1142-4038-8B25-18F5C709C5FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E2980C-AA0A-411C-AF18-A8930099E293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1610" yWindow="1570" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="target" sheetId="1" r:id="rId1"/>
+    <sheet name="list" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
